--- a/Data/EC/NIT-9009787128.xlsx
+++ b/Data/EC/NIT-9009787128.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B8E32C2-E9E9-4674-8C71-EA4F5E220C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{859C0A42-9362-4AF5-926D-7A1A6982FB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{FEDE67F1-4913-4F1E-89FA-ED15FB264B1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{54B0F9AE-9A5C-4977-B839-F4CD10EE6857}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="141">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>MARIA JOSE VELASQUEZ SIERRA</t>
+  </si>
+  <si>
+    <t>2607</t>
   </si>
   <si>
     <t>2606</t>
@@ -824,22 +827,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AE91746-E26D-C02C-BA50-E11F00E6AB19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F46A91BE-7969-68BE-C832-697095D13E68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -848,7 +851,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -861,7 +864,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1190,27 +1193,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E58D84B-6FDB-41FF-8679-2A6C5B2B1A16}">
-  <dimension ref="B2:J387"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD44F6EB-DCE8-470F-9124-D93523DCA961}">
+  <dimension ref="B2:J391"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1219,7 +1222,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1230,7 +1233,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1241,7 +1244,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1252,10 +1255,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1268,8 +1271,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1284,15 +1287,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>16660375</v>
+        <v>16841971</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1300,27 +1303,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="5">
         <v>13</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F13" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1340,16 +1343,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="J15" s="14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1375,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1398,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1421,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1441,7 +1444,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1464,7 +1467,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1490,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1510,7 +1513,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1533,7 +1536,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1559,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1582,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1605,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1625,7 +1628,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1648,7 +1651,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1671,7 +1674,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1697,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1717,7 +1720,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1743,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1766,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1789,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1812,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1832,7 +1835,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1858,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1878,7 +1881,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1901,7 +1904,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1924,7 +1927,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1947,7 +1950,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1973,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +1996,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -2016,7 +2019,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2042,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2062,7 +2065,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2088,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2111,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2131,7 +2134,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2154,7 +2157,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2177,7 +2180,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2200,7 +2203,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2223,7 +2226,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2249,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2269,7 +2272,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2292,7 +2295,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2315,7 +2318,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2338,7 +2341,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2361,7 +2364,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2384,7 +2387,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2410,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2430,7 +2433,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2453,7 +2456,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2476,7 +2479,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2499,7 +2502,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2522,7 +2525,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2545,7 +2548,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2571,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2591,7 +2594,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2614,7 +2617,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2637,7 +2640,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2660,7 +2663,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2683,7 +2686,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2706,7 +2709,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2729,7 +2732,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2752,7 +2755,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2763,7 +2766,7 @@
         <v>13</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F77" s="18">
         <v>40000</v>
@@ -2775,7 +2778,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2786,7 +2789,7 @@
         <v>13</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="F78" s="18">
         <v>40000</v>
@@ -2798,7 +2801,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2821,7 +2824,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2844,7 +2847,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2867,7 +2870,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2890,7 +2893,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2913,7 +2916,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2936,7 +2939,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2959,7 +2962,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2982,7 +2985,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -3005,7 +3008,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -3028,7 +3031,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -3051,7 +3054,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +3077,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3097,7 +3100,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3120,7 +3123,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3143,7 +3146,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3166,7 +3169,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3189,7 +3192,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3212,7 +3215,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3235,7 +3238,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3258,7 +3261,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3281,7 +3284,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3304,7 +3307,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3327,7 +3330,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3350,7 +3353,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3373,7 +3376,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3396,7 +3399,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3419,41 +3422,41 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E106" s="16" t="s">
-        <v>73</v>
-      </c>
       <c r="F106" s="18">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="G106" s="18">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="H106" s="19"/>
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F107" s="18">
         <v>60000</v>
@@ -3465,18 +3468,18 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="F108" s="18">
         <v>60000</v>
@@ -3488,15 +3491,15 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E109" s="16" t="s">
         <v>75</v>
@@ -3511,15 +3514,15 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E110" s="16" t="s">
         <v>76</v>
@@ -3534,15 +3537,15 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E111" s="16" t="s">
         <v>77</v>
@@ -3557,15 +3560,15 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E112" s="16" t="s">
         <v>78</v>
@@ -3580,21 +3583,21 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E113" s="16" t="s">
         <v>79</v>
       </c>
       <c r="F113" s="18">
-        <v>28000</v>
+        <v>60000</v>
       </c>
       <c r="G113" s="18">
         <v>1500000</v>
@@ -3603,87 +3606,87 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D114" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D114" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="E114" s="16" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="F114" s="18">
-        <v>39600</v>
+        <v>28000</v>
       </c>
       <c r="G114" s="18">
-        <v>1100000</v>
+        <v>1500000</v>
       </c>
       <c r="H114" s="19"/>
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C115" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D115" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D115" s="17" t="s">
-        <v>107</v>
-      </c>
       <c r="E115" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F115" s="18">
-        <v>25600</v>
+        <v>39600</v>
       </c>
       <c r="G115" s="18">
-        <v>1200000</v>
+        <v>1100000</v>
       </c>
       <c r="H115" s="19"/>
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C116" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D116" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D116" s="17" t="s">
-        <v>109</v>
-      </c>
       <c r="E116" s="16" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="F116" s="18">
-        <v>56000</v>
+        <v>25600</v>
       </c>
       <c r="G116" s="18">
-        <v>1400000</v>
+        <v>1200000</v>
       </c>
       <c r="H116" s="19"/>
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F117" s="18">
         <v>56000</v>
@@ -3695,18 +3698,18 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F118" s="18">
         <v>56000</v>
@@ -3718,18 +3721,18 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F119" s="18">
         <v>56000</v>
@@ -3741,18 +3744,18 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F120" s="18">
         <v>56000</v>
@@ -3764,18 +3767,18 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F121" s="18">
         <v>56000</v>
@@ -3787,18 +3790,18 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F122" s="18">
         <v>56000</v>
@@ -3810,18 +3813,18 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F123" s="18">
         <v>56000</v>
@@ -3833,18 +3836,18 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F124" s="18">
         <v>56000</v>
@@ -3856,18 +3859,18 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F125" s="18">
         <v>56000</v>
@@ -3879,18 +3882,18 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F126" s="18">
         <v>56000</v>
@@ -3902,18 +3905,18 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E127" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F127" s="18">
         <v>56000</v>
@@ -3925,18 +3928,18 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E128" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F128" s="18">
         <v>56000</v>
@@ -3948,18 +3951,18 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F129" s="18">
         <v>56000</v>
@@ -3971,18 +3974,18 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F130" s="18">
         <v>56000</v>
@@ -3994,18 +3997,18 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F131" s="18">
         <v>56000</v>
@@ -4017,18 +4020,18 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F132" s="18">
         <v>56000</v>
@@ -4040,18 +4043,18 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F133" s="18">
         <v>56000</v>
@@ -4063,18 +4066,18 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F134" s="18">
         <v>56000</v>
@@ -4086,18 +4089,18 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F135" s="18">
         <v>56000</v>
@@ -4109,18 +4112,18 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F136" s="18">
         <v>56000</v>
@@ -4132,18 +4135,18 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F137" s="18">
         <v>56000</v>
@@ -4155,18 +4158,18 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F138" s="18">
         <v>56000</v>
@@ -4178,18 +4181,18 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F139" s="18">
         <v>56000</v>
@@ -4201,18 +4204,18 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F140" s="18">
         <v>56000</v>
@@ -4224,18 +4227,18 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F141" s="18">
         <v>56000</v>
@@ -4247,18 +4250,18 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E142" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F142" s="18">
         <v>56000</v>
@@ -4270,18 +4273,18 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E143" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F143" s="18">
         <v>56000</v>
@@ -4293,18 +4296,18 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E144" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F144" s="18">
         <v>56000</v>
@@ -4316,18 +4319,18 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E145" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F145" s="18">
         <v>56000</v>
@@ -4339,18 +4342,18 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E146" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F146" s="18">
         <v>56000</v>
@@ -4362,18 +4365,18 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F147" s="18">
         <v>56000</v>
@@ -4385,18 +4388,18 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F148" s="18">
         <v>56000</v>
@@ -4408,18 +4411,18 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F149" s="18">
         <v>56000</v>
@@ -4431,18 +4434,18 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E150" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F150" s="18">
         <v>56000</v>
@@ -4454,18 +4457,18 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F151" s="18">
         <v>56000</v>
@@ -4477,18 +4480,18 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E152" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F152" s="18">
         <v>56000</v>
@@ -4500,18 +4503,18 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E153" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F153" s="18">
         <v>56000</v>
@@ -4523,18 +4526,18 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F154" s="18">
         <v>56000</v>
@@ -4546,18 +4549,18 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E155" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F155" s="18">
         <v>56000</v>
@@ -4569,18 +4572,18 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C156" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F156" s="18">
         <v>56000</v>
@@ -4592,18 +4595,18 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E157" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F157" s="18">
         <v>56000</v>
@@ -4615,18 +4618,18 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E158" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F158" s="18">
         <v>56000</v>
@@ -4638,18 +4641,18 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F159" s="18">
         <v>56000</v>
@@ -4661,18 +4664,18 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E160" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F160" s="18">
         <v>56000</v>
@@ -4684,18 +4687,18 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E161" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F161" s="18">
         <v>56000</v>
@@ -4707,18 +4710,18 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F162" s="18">
         <v>56000</v>
@@ -4730,18 +4733,18 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F163" s="18">
         <v>56000</v>
@@ -4753,18 +4756,18 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E164" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F164" s="18">
         <v>56000</v>
@@ -4776,18 +4779,18 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F165" s="18">
         <v>56000</v>
@@ -4799,18 +4802,18 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E166" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F166" s="18">
         <v>56000</v>
@@ -4822,18 +4825,18 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C167" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F167" s="18">
         <v>56000</v>
@@ -4845,18 +4848,18 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C168" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E168" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F168" s="18">
         <v>56000</v>
@@ -4868,18 +4871,18 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C169" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F169" s="18">
         <v>56000</v>
@@ -4891,18 +4894,18 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E170" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F170" s="18">
         <v>56000</v>
@@ -4914,18 +4917,18 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F171" s="18">
         <v>56000</v>
@@ -4937,18 +4940,18 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C172" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F172" s="18">
         <v>56000</v>
@@ -4960,18 +4963,18 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C173" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F173" s="18">
         <v>56000</v>
@@ -4983,18 +4986,18 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F174" s="18">
         <v>56000</v>
@@ -5006,18 +5009,18 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F175" s="18">
         <v>56000</v>
@@ -5029,18 +5032,18 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C176" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E176" s="16" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F176" s="18">
         <v>56000</v>
@@ -5052,15 +5055,15 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E177" s="16" t="s">
         <v>74</v>
@@ -5075,18 +5078,18 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C178" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="F178" s="18">
         <v>56000</v>
@@ -5098,18 +5101,18 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F179" s="18">
         <v>56000</v>
@@ -5121,18 +5124,18 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F180" s="18">
         <v>56000</v>
@@ -5144,18 +5147,18 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E181" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F181" s="18">
         <v>56000</v>
@@ -5167,18 +5170,18 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E182" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F182" s="18">
         <v>56000</v>
@@ -5190,18 +5193,18 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D183" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E183" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F183" s="18">
         <v>56000</v>
@@ -5213,18 +5216,18 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C184" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D184" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E184" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F184" s="18">
         <v>56000</v>
@@ -5236,18 +5239,18 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C185" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E185" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F185" s="18">
         <v>56000</v>
@@ -5259,18 +5262,18 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E186" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F186" s="18">
         <v>56000</v>
@@ -5282,18 +5285,18 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C187" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E187" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F187" s="18">
         <v>56000</v>
@@ -5305,18 +5308,18 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C188" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E188" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F188" s="18">
         <v>56000</v>
@@ -5328,18 +5331,18 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C189" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F189" s="18">
         <v>56000</v>
@@ -5351,18 +5354,18 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C190" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E190" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F190" s="18">
         <v>56000</v>
@@ -5374,18 +5377,18 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C191" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F191" s="18">
         <v>56000</v>
@@ -5397,18 +5400,18 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C192" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E192" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F192" s="18">
         <v>56000</v>
@@ -5420,18 +5423,18 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C193" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D193" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E193" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F193" s="18">
         <v>56000</v>
@@ -5443,18 +5446,18 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C194" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E194" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F194" s="18">
         <v>56000</v>
@@ -5466,18 +5469,18 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C195" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D195" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F195" s="18">
         <v>56000</v>
@@ -5489,18 +5492,18 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C196" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E196" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F196" s="18">
         <v>56000</v>
@@ -5512,18 +5515,18 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C197" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E197" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F197" s="18">
         <v>56000</v>
@@ -5535,18 +5538,18 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C198" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F198" s="18">
         <v>56000</v>
@@ -5558,18 +5561,18 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C199" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E199" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F199" s="18">
         <v>56000</v>
@@ -5581,18 +5584,18 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C200" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D200" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F200" s="18">
         <v>56000</v>
@@ -5604,18 +5607,18 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C201" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E201" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F201" s="18">
         <v>56000</v>
@@ -5627,18 +5630,18 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C202" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F202" s="18">
         <v>56000</v>
@@ -5650,18 +5653,18 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C203" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F203" s="18">
         <v>56000</v>
@@ -5673,18 +5676,18 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C204" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F204" s="18">
         <v>56000</v>
@@ -5696,18 +5699,18 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C205" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E205" s="16" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F205" s="18">
         <v>56000</v>
@@ -5719,21 +5722,21 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C206" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E206" s="16" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F206" s="18">
-        <v>44800</v>
+        <v>56000</v>
       </c>
       <c r="G206" s="18">
         <v>1400000</v>
@@ -5742,64 +5745,64 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="F207" s="18">
-        <v>33125</v>
+        <v>56000</v>
       </c>
       <c r="G207" s="18">
-        <v>828116</v>
+        <v>1400000</v>
       </c>
       <c r="H207" s="19"/>
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C208" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D208" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E208" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D208" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E208" s="16" t="s">
-        <v>15</v>
-      </c>
       <c r="F208" s="18">
-        <v>33125</v>
+        <v>44800</v>
       </c>
       <c r="G208" s="18">
-        <v>828116</v>
+        <v>1400000</v>
       </c>
       <c r="H208" s="19"/>
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C209" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E209" s="16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F209" s="18">
         <v>33125</v>
@@ -5811,18 +5814,18 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C210" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D210" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F210" s="18">
         <v>33125</v>
@@ -5834,18 +5837,18 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C211" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D211" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E211" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F211" s="18">
         <v>33125</v>
@@ -5857,18 +5860,18 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C212" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D212" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E212" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F212" s="18">
         <v>33125</v>
@@ -5880,18 +5883,18 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C213" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D213" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E213" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F213" s="18">
         <v>33125</v>
@@ -5903,18 +5906,18 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C214" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D214" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F214" s="18">
         <v>33125</v>
@@ -5926,18 +5929,18 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C215" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D215" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F215" s="18">
         <v>33125</v>
@@ -5949,18 +5952,18 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C216" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E216" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F216" s="18">
         <v>33125</v>
@@ -5972,18 +5975,18 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F217" s="18">
         <v>33125</v>
@@ -5995,18 +5998,18 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C218" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E218" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F218" s="18">
         <v>33125</v>
@@ -6018,18 +6021,18 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C219" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D219" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E219" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F219" s="18">
         <v>33125</v>
@@ -6041,18 +6044,18 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C220" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D220" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E220" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F220" s="18">
         <v>33125</v>
@@ -6064,18 +6067,18 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C221" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D221" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E221" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F221" s="18">
         <v>33125</v>
@@ -6087,18 +6090,18 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C222" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D222" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E222" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F222" s="18">
         <v>33125</v>
@@ -6110,18 +6113,18 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C223" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D223" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E223" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F223" s="18">
         <v>33125</v>
@@ -6133,18 +6136,18 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C224" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D224" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E224" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F224" s="18">
         <v>33125</v>
@@ -6156,18 +6159,18 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C225" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D225" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E225" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F225" s="18">
         <v>33125</v>
@@ -6179,18 +6182,18 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C226" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D226" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E226" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F226" s="18">
         <v>33125</v>
@@ -6202,18 +6205,18 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C227" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D227" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E227" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F227" s="18">
         <v>33125</v>
@@ -6225,18 +6228,18 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C228" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D228" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E228" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F228" s="18">
         <v>33125</v>
@@ -6248,18 +6251,18 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C229" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D229" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F229" s="18">
         <v>33125</v>
@@ -6271,18 +6274,18 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C230" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D230" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E230" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F230" s="18">
         <v>33125</v>
@@ -6294,18 +6297,18 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C231" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D231" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E231" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F231" s="18">
         <v>33125</v>
@@ -6317,18 +6320,18 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C232" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D232" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E232" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F232" s="18">
         <v>33125</v>
@@ -6340,18 +6343,18 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C233" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D233" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E233" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F233" s="18">
         <v>33125</v>
@@ -6363,18 +6366,18 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C234" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D234" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E234" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F234" s="18">
         <v>33125</v>
@@ -6386,18 +6389,18 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C235" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D235" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E235" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F235" s="18">
         <v>33125</v>
@@ -6409,18 +6412,18 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C236" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D236" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E236" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F236" s="18">
         <v>33125</v>
@@ -6432,18 +6435,18 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C237" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D237" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E237" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F237" s="18">
         <v>33125</v>
@@ -6455,18 +6458,18 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C238" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D238" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E238" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F238" s="18">
         <v>33125</v>
@@ -6478,18 +6481,18 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C239" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D239" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E239" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F239" s="18">
         <v>33125</v>
@@ -6501,18 +6504,18 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C240" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D240" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E240" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F240" s="18">
         <v>33125</v>
@@ -6524,18 +6527,18 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C241" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D241" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E241" s="16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F241" s="18">
         <v>33125</v>
@@ -6547,18 +6550,18 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C242" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D242" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E242" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F242" s="18">
         <v>33125</v>
@@ -6570,18 +6573,18 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C243" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D243" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E243" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F243" s="18">
         <v>33125</v>
@@ -6593,18 +6596,18 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C244" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D244" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E244" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F244" s="18">
         <v>33125</v>
@@ -6616,18 +6619,18 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C245" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D245" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E245" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F245" s="18">
         <v>33125</v>
@@ -6639,18 +6642,18 @@
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C246" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D246" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E246" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F246" s="18">
         <v>33125</v>
@@ -6662,18 +6665,18 @@
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C247" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D247" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E247" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F247" s="18">
         <v>33125</v>
@@ -6685,18 +6688,18 @@
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C248" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D248" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E248" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F248" s="18">
         <v>33125</v>
@@ -6708,18 +6711,18 @@
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C249" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D249" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E249" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F249" s="18">
         <v>33125</v>
@@ -6731,18 +6734,18 @@
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C250" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D250" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E250" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F250" s="18">
         <v>33125</v>
@@ -6754,18 +6757,18 @@
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C251" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D251" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E251" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F251" s="18">
         <v>33125</v>
@@ -6777,18 +6780,18 @@
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C252" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D252" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E252" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F252" s="18">
         <v>33125</v>
@@ -6800,18 +6803,18 @@
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C253" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D253" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E253" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F253" s="18">
         <v>33125</v>
@@ -6823,18 +6826,18 @@
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C254" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D254" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E254" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F254" s="18">
         <v>33125</v>
@@ -6846,18 +6849,18 @@
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C255" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D255" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E255" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F255" s="18">
         <v>33125</v>
@@ -6869,18 +6872,18 @@
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C256" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D256" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E256" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F256" s="18">
         <v>33125</v>
@@ -6892,18 +6895,18 @@
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C257" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D257" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E257" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F257" s="18">
         <v>33125</v>
@@ -6915,18 +6918,18 @@
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C258" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D258" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E258" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F258" s="18">
         <v>33125</v>
@@ -6938,18 +6941,18 @@
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C259" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D259" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E259" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F259" s="18">
         <v>33125</v>
@@ -6961,18 +6964,18 @@
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C260" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D260" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F260" s="18">
         <v>33125</v>
@@ -6984,18 +6987,18 @@
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C261" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D261" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E261" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F261" s="18">
         <v>33125</v>
@@ -7007,18 +7010,18 @@
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C262" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D262" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E262" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F262" s="18">
         <v>33125</v>
@@ -7030,18 +7033,18 @@
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C263" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D263" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E263" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F263" s="18">
         <v>33125</v>
@@ -7053,18 +7056,18 @@
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C264" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D264" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E264" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F264" s="18">
         <v>33125</v>
@@ -7076,18 +7079,18 @@
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C265" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D265" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E265" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F265" s="18">
         <v>33125</v>
@@ -7099,18 +7102,18 @@
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C266" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D266" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E266" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F266" s="18">
         <v>33125</v>
@@ -7122,18 +7125,18 @@
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C267" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D267" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E267" s="16" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="F267" s="18">
         <v>33125</v>
@@ -7145,18 +7148,18 @@
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C268" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D268" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E268" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F268" s="18">
         <v>33125</v>
@@ -7168,18 +7171,18 @@
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C269" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D269" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E269" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F269" s="18">
         <v>33125</v>
@@ -7191,18 +7194,18 @@
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C270" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D270" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E270" s="16" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="F270" s="18">
         <v>33125</v>
@@ -7214,18 +7217,18 @@
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C271" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D271" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E271" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F271" s="18">
         <v>33125</v>
@@ -7237,18 +7240,18 @@
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C272" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D272" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E272" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F272" s="18">
         <v>33125</v>
@@ -7260,18 +7263,18 @@
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C273" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D273" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E273" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F273" s="18">
         <v>33125</v>
@@ -7283,18 +7286,18 @@
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C274" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D274" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E274" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F274" s="18">
         <v>33125</v>
@@ -7306,18 +7309,18 @@
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C275" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D275" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E275" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F275" s="18">
         <v>33125</v>
@@ -7329,18 +7332,18 @@
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C276" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D276" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E276" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F276" s="18">
         <v>33125</v>
@@ -7352,18 +7355,18 @@
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C277" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D277" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E277" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F277" s="18">
         <v>33125</v>
@@ -7375,18 +7378,18 @@
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C278" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D278" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E278" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F278" s="18">
         <v>33125</v>
@@ -7398,18 +7401,18 @@
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C279" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D279" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E279" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F279" s="18">
         <v>33125</v>
@@ -7421,18 +7424,18 @@
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C280" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D280" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E280" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F280" s="18">
         <v>33125</v>
@@ -7444,18 +7447,18 @@
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C281" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D281" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E281" s="16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F281" s="18">
         <v>33125</v>
@@ -7467,18 +7470,18 @@
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C282" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D282" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E282" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F282" s="18">
         <v>33125</v>
@@ -7490,18 +7493,18 @@
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C283" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D283" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E283" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F283" s="18">
         <v>33125</v>
@@ -7513,18 +7516,18 @@
       <c r="I283" s="19"/>
       <c r="J283" s="20"/>
     </row>
-    <row r="284" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="284" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B284" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C284" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D284" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E284" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F284" s="18">
         <v>33125</v>
@@ -7536,18 +7539,18 @@
       <c r="I284" s="19"/>
       <c r="J284" s="20"/>
     </row>
-    <row r="285" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="285" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B285" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C285" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D285" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E285" s="16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F285" s="18">
         <v>33125</v>
@@ -7559,156 +7562,156 @@
       <c r="I285" s="19"/>
       <c r="J285" s="20"/>
     </row>
-    <row r="286" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="286" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B286" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C286" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D286" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D286" s="17" t="s">
-        <v>115</v>
-      </c>
       <c r="E286" s="16" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F286" s="18">
-        <v>1600</v>
+        <v>33125</v>
       </c>
       <c r="G286" s="18">
-        <v>1200000</v>
+        <v>828116</v>
       </c>
       <c r="H286" s="19"/>
       <c r="I286" s="19"/>
       <c r="J286" s="20"/>
     </row>
-    <row r="287" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="287" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B287" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C287" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D287" s="17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E287" s="16" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="F287" s="18">
-        <v>3208</v>
+        <v>33125</v>
       </c>
       <c r="G287" s="18">
-        <v>1202968</v>
+        <v>828116</v>
       </c>
       <c r="H287" s="19"/>
       <c r="I287" s="19"/>
       <c r="J287" s="20"/>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C288" s="16" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D288" s="17" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E288" s="16" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="F288" s="18">
-        <v>29509</v>
+        <v>33125</v>
       </c>
       <c r="G288" s="18">
-        <v>737717</v>
+        <v>828116</v>
       </c>
       <c r="H288" s="19"/>
       <c r="I288" s="19"/>
       <c r="J288" s="20"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B289" s="15" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="C289" s="16" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D289" s="17" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E289" s="16" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="F289" s="18">
-        <v>52471</v>
+        <v>1600</v>
       </c>
       <c r="G289" s="18">
-        <v>1311789</v>
+        <v>1200000</v>
       </c>
       <c r="H289" s="19"/>
       <c r="I289" s="19"/>
       <c r="J289" s="20"/>
     </row>
-    <row r="290" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="290" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B290" s="15" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="C290" s="16" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D290" s="17" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E290" s="16" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="F290" s="18">
-        <v>52471</v>
+        <v>3208</v>
       </c>
       <c r="G290" s="18">
-        <v>1311789</v>
+        <v>1202968</v>
       </c>
       <c r="H290" s="19"/>
       <c r="I290" s="19"/>
       <c r="J290" s="20"/>
     </row>
-    <row r="291" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="291" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B291" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C291" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D291" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E291" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C291" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D291" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E291" s="16" t="s">
-        <v>16</v>
-      </c>
       <c r="F291" s="18">
-        <v>52471</v>
+        <v>29509</v>
       </c>
       <c r="G291" s="18">
-        <v>1311789</v>
+        <v>737717</v>
       </c>
       <c r="H291" s="19"/>
       <c r="I291" s="19"/>
       <c r="J291" s="20"/>
     </row>
-    <row r="292" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="292" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B292" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C292" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D292" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E292" s="16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F292" s="18">
         <v>52471</v>
@@ -7720,18 +7723,18 @@
       <c r="I292" s="19"/>
       <c r="J292" s="20"/>
     </row>
-    <row r="293" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="293" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B293" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C293" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D293" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E293" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F293" s="18">
         <v>52471</v>
@@ -7743,18 +7746,18 @@
       <c r="I293" s="19"/>
       <c r="J293" s="20"/>
     </row>
-    <row r="294" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="294" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B294" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C294" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D294" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E294" s="16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F294" s="18">
         <v>52471</v>
@@ -7766,18 +7769,18 @@
       <c r="I294" s="19"/>
       <c r="J294" s="20"/>
     </row>
-    <row r="295" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="295" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B295" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C295" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D295" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E295" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F295" s="18">
         <v>52471</v>
@@ -7789,18 +7792,18 @@
       <c r="I295" s="19"/>
       <c r="J295" s="20"/>
     </row>
-    <row r="296" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="296" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B296" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C296" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D296" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E296" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F296" s="18">
         <v>52471</v>
@@ -7812,18 +7815,18 @@
       <c r="I296" s="19"/>
       <c r="J296" s="20"/>
     </row>
-    <row r="297" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="297" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B297" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C297" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D297" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E297" s="16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F297" s="18">
         <v>52471</v>
@@ -7835,18 +7838,18 @@
       <c r="I297" s="19"/>
       <c r="J297" s="20"/>
     </row>
-    <row r="298" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="298" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B298" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C298" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D298" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E298" s="16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F298" s="18">
         <v>52471</v>
@@ -7858,18 +7861,18 @@
       <c r="I298" s="19"/>
       <c r="J298" s="20"/>
     </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="299" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B299" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C299" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D299" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E299" s="16" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F299" s="18">
         <v>52471</v>
@@ -7881,18 +7884,18 @@
       <c r="I299" s="19"/>
       <c r="J299" s="20"/>
     </row>
-    <row r="300" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="300" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B300" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C300" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D300" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E300" s="16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F300" s="18">
         <v>52471</v>
@@ -7904,18 +7907,18 @@
       <c r="I300" s="19"/>
       <c r="J300" s="20"/>
     </row>
-    <row r="301" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="301" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B301" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C301" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D301" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E301" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F301" s="18">
         <v>52471</v>
@@ -7927,18 +7930,18 @@
       <c r="I301" s="19"/>
       <c r="J301" s="20"/>
     </row>
-    <row r="302" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="302" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B302" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C302" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D302" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E302" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F302" s="18">
         <v>52471</v>
@@ -7950,18 +7953,18 @@
       <c r="I302" s="19"/>
       <c r="J302" s="20"/>
     </row>
-    <row r="303" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="303" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B303" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C303" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D303" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E303" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F303" s="18">
         <v>52471</v>
@@ -7973,18 +7976,18 @@
       <c r="I303" s="19"/>
       <c r="J303" s="20"/>
     </row>
-    <row r="304" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="304" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B304" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C304" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D304" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E304" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F304" s="18">
         <v>52471</v>
@@ -7996,18 +7999,18 @@
       <c r="I304" s="19"/>
       <c r="J304" s="20"/>
     </row>
-    <row r="305" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="305" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B305" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C305" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D305" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E305" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F305" s="18">
         <v>52471</v>
@@ -8019,18 +8022,18 @@
       <c r="I305" s="19"/>
       <c r="J305" s="20"/>
     </row>
-    <row r="306" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="306" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B306" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C306" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D306" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E306" s="16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F306" s="18">
         <v>52471</v>
@@ -8042,18 +8045,18 @@
       <c r="I306" s="19"/>
       <c r="J306" s="20"/>
     </row>
-    <row r="307" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="307" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B307" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C307" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D307" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E307" s="16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F307" s="18">
         <v>52471</v>
@@ -8065,18 +8068,18 @@
       <c r="I307" s="19"/>
       <c r="J307" s="20"/>
     </row>
-    <row r="308" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="308" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B308" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C308" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D308" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E308" s="16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F308" s="18">
         <v>52471</v>
@@ -8088,18 +8091,18 @@
       <c r="I308" s="19"/>
       <c r="J308" s="20"/>
     </row>
-    <row r="309" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="309" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B309" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C309" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D309" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E309" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F309" s="18">
         <v>52471</v>
@@ -8111,18 +8114,18 @@
       <c r="I309" s="19"/>
       <c r="J309" s="20"/>
     </row>
-    <row r="310" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="310" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B310" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C310" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D310" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E310" s="16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F310" s="18">
         <v>52471</v>
@@ -8134,18 +8137,18 @@
       <c r="I310" s="19"/>
       <c r="J310" s="20"/>
     </row>
-    <row r="311" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="311" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B311" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C311" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D311" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E311" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F311" s="18">
         <v>52471</v>
@@ -8157,18 +8160,18 @@
       <c r="I311" s="19"/>
       <c r="J311" s="20"/>
     </row>
-    <row r="312" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="312" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B312" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C312" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D312" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E312" s="16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F312" s="18">
         <v>52471</v>
@@ -8180,18 +8183,18 @@
       <c r="I312" s="19"/>
       <c r="J312" s="20"/>
     </row>
-    <row r="313" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="313" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B313" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C313" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D313" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E313" s="16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F313" s="18">
         <v>52471</v>
@@ -8203,18 +8206,18 @@
       <c r="I313" s="19"/>
       <c r="J313" s="20"/>
     </row>
-    <row r="314" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="314" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B314" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C314" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D314" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E314" s="16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F314" s="18">
         <v>52471</v>
@@ -8226,18 +8229,18 @@
       <c r="I314" s="19"/>
       <c r="J314" s="20"/>
     </row>
-    <row r="315" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="315" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B315" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C315" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D315" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E315" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F315" s="18">
         <v>52471</v>
@@ -8249,18 +8252,18 @@
       <c r="I315" s="19"/>
       <c r="J315" s="20"/>
     </row>
-    <row r="316" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="316" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B316" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C316" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D316" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E316" s="16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F316" s="18">
         <v>52471</v>
@@ -8272,18 +8275,18 @@
       <c r="I316" s="19"/>
       <c r="J316" s="20"/>
     </row>
-    <row r="317" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="317" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B317" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C317" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D317" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E317" s="16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F317" s="18">
         <v>52471</v>
@@ -8295,18 +8298,18 @@
       <c r="I317" s="19"/>
       <c r="J317" s="20"/>
     </row>
-    <row r="318" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="318" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B318" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C318" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D318" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E318" s="16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F318" s="18">
         <v>52471</v>
@@ -8318,18 +8321,18 @@
       <c r="I318" s="19"/>
       <c r="J318" s="20"/>
     </row>
-    <row r="319" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="319" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B319" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C319" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D319" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E319" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F319" s="18">
         <v>52471</v>
@@ -8341,18 +8344,18 @@
       <c r="I319" s="19"/>
       <c r="J319" s="20"/>
     </row>
-    <row r="320" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="320" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B320" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C320" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D320" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E320" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F320" s="18">
         <v>52471</v>
@@ -8364,18 +8367,18 @@
       <c r="I320" s="19"/>
       <c r="J320" s="20"/>
     </row>
-    <row r="321" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="321" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B321" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C321" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D321" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E321" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F321" s="18">
         <v>52471</v>
@@ -8387,18 +8390,18 @@
       <c r="I321" s="19"/>
       <c r="J321" s="20"/>
     </row>
-    <row r="322" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="322" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B322" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C322" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D322" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E322" s="16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F322" s="18">
         <v>52471</v>
@@ -8410,18 +8413,18 @@
       <c r="I322" s="19"/>
       <c r="J322" s="20"/>
     </row>
-    <row r="323" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="323" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B323" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C323" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D323" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E323" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F323" s="18">
         <v>52471</v>
@@ -8433,18 +8436,18 @@
       <c r="I323" s="19"/>
       <c r="J323" s="20"/>
     </row>
-    <row r="324" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="324" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B324" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C324" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D324" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E324" s="16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F324" s="18">
         <v>52471</v>
@@ -8456,18 +8459,18 @@
       <c r="I324" s="19"/>
       <c r="J324" s="20"/>
     </row>
-    <row r="325" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="325" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B325" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C325" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D325" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E325" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F325" s="18">
         <v>52471</v>
@@ -8479,18 +8482,18 @@
       <c r="I325" s="19"/>
       <c r="J325" s="20"/>
     </row>
-    <row r="326" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="326" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B326" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C326" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D326" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E326" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F326" s="18">
         <v>52471</v>
@@ -8502,18 +8505,18 @@
       <c r="I326" s="19"/>
       <c r="J326" s="20"/>
     </row>
-    <row r="327" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="327" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B327" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C327" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D327" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E327" s="16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F327" s="18">
         <v>52471</v>
@@ -8525,18 +8528,18 @@
       <c r="I327" s="19"/>
       <c r="J327" s="20"/>
     </row>
-    <row r="328" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="328" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B328" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C328" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D328" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E328" s="16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F328" s="18">
         <v>52471</v>
@@ -8548,18 +8551,18 @@
       <c r="I328" s="19"/>
       <c r="J328" s="20"/>
     </row>
-    <row r="329" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="329" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B329" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C329" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D329" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E329" s="16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F329" s="18">
         <v>52471</v>
@@ -8571,18 +8574,18 @@
       <c r="I329" s="19"/>
       <c r="J329" s="20"/>
     </row>
-    <row r="330" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="330" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B330" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C330" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D330" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E330" s="16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F330" s="18">
         <v>52471</v>
@@ -8594,18 +8597,18 @@
       <c r="I330" s="19"/>
       <c r="J330" s="20"/>
     </row>
-    <row r="331" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="331" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B331" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C331" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D331" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E331" s="16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F331" s="18">
         <v>52471</v>
@@ -8617,18 +8620,18 @@
       <c r="I331" s="19"/>
       <c r="J331" s="20"/>
     </row>
-    <row r="332" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="332" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B332" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C332" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D332" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E332" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F332" s="18">
         <v>52471</v>
@@ -8640,18 +8643,18 @@
       <c r="I332" s="19"/>
       <c r="J332" s="20"/>
     </row>
-    <row r="333" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="333" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B333" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C333" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D333" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E333" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F333" s="18">
         <v>52471</v>
@@ -8663,18 +8666,18 @@
       <c r="I333" s="19"/>
       <c r="J333" s="20"/>
     </row>
-    <row r="334" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="334" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B334" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C334" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D334" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E334" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F334" s="18">
         <v>52471</v>
@@ -8686,18 +8689,18 @@
       <c r="I334" s="19"/>
       <c r="J334" s="20"/>
     </row>
-    <row r="335" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="335" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B335" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C335" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D335" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E335" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F335" s="18">
         <v>52471</v>
@@ -8709,18 +8712,18 @@
       <c r="I335" s="19"/>
       <c r="J335" s="20"/>
     </row>
-    <row r="336" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="336" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B336" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C336" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D336" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E336" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F336" s="18">
         <v>52471</v>
@@ -8732,18 +8735,18 @@
       <c r="I336" s="19"/>
       <c r="J336" s="20"/>
     </row>
-    <row r="337" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="337" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B337" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C337" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D337" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E337" s="16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F337" s="18">
         <v>52471</v>
@@ -8755,18 +8758,18 @@
       <c r="I337" s="19"/>
       <c r="J337" s="20"/>
     </row>
-    <row r="338" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="338" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B338" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C338" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D338" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E338" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F338" s="18">
         <v>52471</v>
@@ -8778,18 +8781,18 @@
       <c r="I338" s="19"/>
       <c r="J338" s="20"/>
     </row>
-    <row r="339" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="339" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B339" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C339" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D339" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E339" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F339" s="18">
         <v>52471</v>
@@ -8801,18 +8804,18 @@
       <c r="I339" s="19"/>
       <c r="J339" s="20"/>
     </row>
-    <row r="340" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="340" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B340" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C340" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D340" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E340" s="16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F340" s="18">
         <v>52471</v>
@@ -8824,18 +8827,18 @@
       <c r="I340" s="19"/>
       <c r="J340" s="20"/>
     </row>
-    <row r="341" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="341" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B341" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C341" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D341" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E341" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F341" s="18">
         <v>52471</v>
@@ -8847,18 +8850,18 @@
       <c r="I341" s="19"/>
       <c r="J341" s="20"/>
     </row>
-    <row r="342" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="342" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B342" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C342" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D342" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E342" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F342" s="18">
         <v>52471</v>
@@ -8870,18 +8873,18 @@
       <c r="I342" s="19"/>
       <c r="J342" s="20"/>
     </row>
-    <row r="343" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="343" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B343" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C343" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D343" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E343" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F343" s="18">
         <v>52471</v>
@@ -8893,18 +8896,18 @@
       <c r="I343" s="19"/>
       <c r="J343" s="20"/>
     </row>
-    <row r="344" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="344" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B344" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C344" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D344" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E344" s="16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F344" s="18">
         <v>52471</v>
@@ -8916,18 +8919,18 @@
       <c r="I344" s="19"/>
       <c r="J344" s="20"/>
     </row>
-    <row r="345" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="345" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B345" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C345" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D345" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E345" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F345" s="18">
         <v>52471</v>
@@ -8939,18 +8942,18 @@
       <c r="I345" s="19"/>
       <c r="J345" s="20"/>
     </row>
-    <row r="346" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="346" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B346" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C346" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D346" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E346" s="16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F346" s="18">
         <v>52471</v>
@@ -8962,18 +8965,18 @@
       <c r="I346" s="19"/>
       <c r="J346" s="20"/>
     </row>
-    <row r="347" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="347" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B347" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C347" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D347" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E347" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F347" s="18">
         <v>52471</v>
@@ -8985,18 +8988,18 @@
       <c r="I347" s="19"/>
       <c r="J347" s="20"/>
     </row>
-    <row r="348" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="348" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B348" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C348" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D348" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E348" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F348" s="18">
         <v>52471</v>
@@ -9008,18 +9011,18 @@
       <c r="I348" s="19"/>
       <c r="J348" s="20"/>
     </row>
-    <row r="349" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="349" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B349" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C349" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D349" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E349" s="16" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F349" s="18">
         <v>52471</v>
@@ -9031,18 +9034,18 @@
       <c r="I349" s="19"/>
       <c r="J349" s="20"/>
     </row>
-    <row r="350" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="350" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B350" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C350" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D350" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E350" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F350" s="18">
         <v>52471</v>
@@ -9054,18 +9057,18 @@
       <c r="I350" s="19"/>
       <c r="J350" s="20"/>
     </row>
-    <row r="351" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="351" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B351" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C351" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D351" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E351" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F351" s="18">
         <v>52471</v>
@@ -9077,18 +9080,18 @@
       <c r="I351" s="19"/>
       <c r="J351" s="20"/>
     </row>
-    <row r="352" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="352" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B352" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C352" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D352" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E352" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F352" s="18">
         <v>52471</v>
@@ -9100,18 +9103,18 @@
       <c r="I352" s="19"/>
       <c r="J352" s="20"/>
     </row>
-    <row r="353" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="353" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B353" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C353" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D353" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E353" s="16" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="F353" s="18">
         <v>52471</v>
@@ -9123,18 +9126,18 @@
       <c r="I353" s="19"/>
       <c r="J353" s="20"/>
     </row>
-    <row r="354" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="354" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B354" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C354" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D354" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E354" s="16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F354" s="18">
         <v>52471</v>
@@ -9146,18 +9149,18 @@
       <c r="I354" s="19"/>
       <c r="J354" s="20"/>
     </row>
-    <row r="355" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="355" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B355" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C355" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D355" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E355" s="16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F355" s="18">
         <v>52471</v>
@@ -9169,18 +9172,18 @@
       <c r="I355" s="19"/>
       <c r="J355" s="20"/>
     </row>
-    <row r="356" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="356" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B356" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C356" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D356" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E356" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F356" s="18">
         <v>52471</v>
@@ -9192,18 +9195,18 @@
       <c r="I356" s="19"/>
       <c r="J356" s="20"/>
     </row>
-    <row r="357" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="357" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B357" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C357" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D357" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E357" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F357" s="18">
         <v>52471</v>
@@ -9215,18 +9218,18 @@
       <c r="I357" s="19"/>
       <c r="J357" s="20"/>
     </row>
-    <row r="358" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="358" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B358" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C358" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D358" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E358" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F358" s="18">
         <v>52471</v>
@@ -9238,18 +9241,18 @@
       <c r="I358" s="19"/>
       <c r="J358" s="20"/>
     </row>
-    <row r="359" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="359" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B359" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C359" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D359" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E359" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F359" s="18">
         <v>52471</v>
@@ -9261,18 +9264,18 @@
       <c r="I359" s="19"/>
       <c r="J359" s="20"/>
     </row>
-    <row r="360" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="360" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B360" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C360" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D360" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E360" s="16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F360" s="18">
         <v>52471</v>
@@ -9284,18 +9287,18 @@
       <c r="I360" s="19"/>
       <c r="J360" s="20"/>
     </row>
-    <row r="361" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="361" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B361" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C361" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D361" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E361" s="16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F361" s="18">
         <v>52471</v>
@@ -9307,18 +9310,18 @@
       <c r="I361" s="19"/>
       <c r="J361" s="20"/>
     </row>
-    <row r="362" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="362" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B362" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C362" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D362" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E362" s="16" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F362" s="18">
         <v>52471</v>
@@ -9330,18 +9333,18 @@
       <c r="I362" s="19"/>
       <c r="J362" s="20"/>
     </row>
-    <row r="363" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="363" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B363" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C363" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D363" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E363" s="16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F363" s="18">
         <v>52471</v>
@@ -9353,18 +9356,18 @@
       <c r="I363" s="19"/>
       <c r="J363" s="20"/>
     </row>
-    <row r="364" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="364" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B364" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C364" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D364" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E364" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F364" s="18">
         <v>52471</v>
@@ -9376,18 +9379,18 @@
       <c r="I364" s="19"/>
       <c r="J364" s="20"/>
     </row>
-    <row r="365" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="365" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B365" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C365" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D365" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E365" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F365" s="18">
         <v>52471</v>
@@ -9399,18 +9402,18 @@
       <c r="I365" s="19"/>
       <c r="J365" s="20"/>
     </row>
-    <row r="366" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="366" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B366" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C366" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D366" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E366" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F366" s="18">
         <v>52471</v>
@@ -9422,18 +9425,18 @@
       <c r="I366" s="19"/>
       <c r="J366" s="20"/>
     </row>
-    <row r="367" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="367" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B367" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C367" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D367" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E367" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F367" s="18">
         <v>52471</v>
@@ -9445,18 +9448,18 @@
       <c r="I367" s="19"/>
       <c r="J367" s="20"/>
     </row>
-    <row r="368" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="368" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B368" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C368" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D368" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E368" s="16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F368" s="18">
         <v>52471</v>
@@ -9468,18 +9471,18 @@
       <c r="I368" s="19"/>
       <c r="J368" s="20"/>
     </row>
-    <row r="369" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="369" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B369" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C369" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D369" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E369" s="16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F369" s="18">
         <v>52471</v>
@@ -9491,18 +9494,18 @@
       <c r="I369" s="19"/>
       <c r="J369" s="20"/>
     </row>
-    <row r="370" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="370" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B370" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C370" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D370" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E370" s="16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F370" s="18">
         <v>52471</v>
@@ -9514,18 +9517,18 @@
       <c r="I370" s="19"/>
       <c r="J370" s="20"/>
     </row>
-    <row r="371" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="371" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B371" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C371" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D371" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E371" s="16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F371" s="18">
         <v>52471</v>
@@ -9537,18 +9540,18 @@
       <c r="I371" s="19"/>
       <c r="J371" s="20"/>
     </row>
-    <row r="372" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="372" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B372" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C372" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D372" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E372" s="16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F372" s="18">
         <v>52471</v>
@@ -9560,18 +9563,18 @@
       <c r="I372" s="19"/>
       <c r="J372" s="20"/>
     </row>
-    <row r="373" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="373" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B373" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C373" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D373" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E373" s="16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F373" s="18">
         <v>52471</v>
@@ -9583,18 +9586,18 @@
       <c r="I373" s="19"/>
       <c r="J373" s="20"/>
     </row>
-    <row r="374" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="374" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B374" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C374" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D374" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E374" s="16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F374" s="18">
         <v>52471</v>
@@ -9606,18 +9609,18 @@
       <c r="I374" s="19"/>
       <c r="J374" s="20"/>
     </row>
-    <row r="375" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="375" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B375" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C375" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D375" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E375" s="16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F375" s="18">
         <v>52471</v>
@@ -9629,18 +9632,18 @@
       <c r="I375" s="19"/>
       <c r="J375" s="20"/>
     </row>
-    <row r="376" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="376" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B376" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C376" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D376" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E376" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F376" s="18">
         <v>52471</v>
@@ -9652,18 +9655,18 @@
       <c r="I376" s="19"/>
       <c r="J376" s="20"/>
     </row>
-    <row r="377" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="377" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B377" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C377" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D377" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E377" s="16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F377" s="18">
         <v>52471</v>
@@ -9675,18 +9678,18 @@
       <c r="I377" s="19"/>
       <c r="J377" s="20"/>
     </row>
-    <row r="378" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="378" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B378" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C378" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D378" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E378" s="16" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F378" s="18">
         <v>52471</v>
@@ -9698,21 +9701,21 @@
       <c r="I378" s="19"/>
       <c r="J378" s="20"/>
     </row>
-    <row r="379" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="379" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B379" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C379" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D379" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E379" s="16" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="F379" s="18">
-        <v>41977</v>
+        <v>52471</v>
       </c>
       <c r="G379" s="18">
         <v>1311789</v>
@@ -9721,80 +9724,172 @@
       <c r="I379" s="19"/>
       <c r="J379" s="20"/>
     </row>
-    <row r="380" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="380" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B380" s="15" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="C380" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D380" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D380" s="17" t="s">
-        <v>125</v>
-      </c>
       <c r="E380" s="16" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F380" s="18">
-        <v>33125</v>
+        <v>52471</v>
       </c>
       <c r="G380" s="18">
-        <v>1495000</v>
+        <v>1311789</v>
       </c>
       <c r="H380" s="19"/>
       <c r="I380" s="19"/>
       <c r="J380" s="20"/>
     </row>
-    <row r="381" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B381" s="21" t="s">
+    <row r="381" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B381" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C381" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D381" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E381" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F381" s="18">
+        <v>52471</v>
+      </c>
+      <c r="G381" s="18">
+        <v>1311789</v>
+      </c>
+      <c r="H381" s="19"/>
+      <c r="I381" s="19"/>
+      <c r="J381" s="20"/>
+    </row>
+    <row r="382" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B382" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C382" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D382" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E382" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F382" s="18">
+        <v>52471</v>
+      </c>
+      <c r="G382" s="18">
+        <v>1311789</v>
+      </c>
+      <c r="H382" s="19"/>
+      <c r="I382" s="19"/>
+      <c r="J382" s="20"/>
+    </row>
+    <row r="383" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B383" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C383" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D383" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E383" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F383" s="18">
+        <v>41977</v>
+      </c>
+      <c r="G383" s="18">
+        <v>1311789</v>
+      </c>
+      <c r="H383" s="19"/>
+      <c r="I383" s="19"/>
+      <c r="J383" s="20"/>
+    </row>
+    <row r="384" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B384" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C384" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D384" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C381" s="22" t="s">
+      <c r="E384" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F384" s="18">
+        <v>33125</v>
+      </c>
+      <c r="G384" s="18">
+        <v>1495000</v>
+      </c>
+      <c r="H384" s="19"/>
+      <c r="I384" s="19"/>
+      <c r="J384" s="20"/>
+    </row>
+    <row r="385" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B385" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="D381" s="23" t="s">
+      <c r="C385" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E381" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="F381" s="24">
+      <c r="D385" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E385" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F385" s="24">
         <v>44000</v>
       </c>
-      <c r="G381" s="24">
+      <c r="G385" s="24">
         <v>1100000</v>
       </c>
-      <c r="H381" s="25"/>
-      <c r="I381" s="25"/>
-      <c r="J381" s="26"/>
-    </row>
-    <row r="386" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B386" s="32" t="s">
+      <c r="H385" s="25"/>
+      <c r="I385" s="25"/>
+      <c r="J385" s="26"/>
+    </row>
+    <row r="390" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B390" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C390" s="32"/>
+      <c r="H390" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I390" s="1"/>
+      <c r="J390" s="1"/>
+    </row>
+    <row r="391" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B391" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C386" s="32"/>
-      <c r="H386" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I386" s="1"/>
-      <c r="J386" s="1"/>
-    </row>
-    <row r="387" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B387" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C387" s="32"/>
-      <c r="H387" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I387" s="1"/>
-      <c r="J387" s="1"/>
+      <c r="C391" s="32"/>
+      <c r="H391" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I391" s="1"/>
+      <c r="J391" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B387:C387"/>
-    <mergeCell ref="B386:C386"/>
-    <mergeCell ref="H387:J387"/>
-    <mergeCell ref="H386:J386"/>
+    <mergeCell ref="B391:C391"/>
+    <mergeCell ref="B390:C390"/>
+    <mergeCell ref="H391:J391"/>
+    <mergeCell ref="H390:J390"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
